--- a/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T10:06:59+00:00</t>
+    <t>2026-08-20T14:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -919,7 +919,7 @@
     <t>Description of clinical condition indicating why the ImagingStudy was requested.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-imagerie-objectif-reference-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-imagerie-objectif-reference-cisis|20260716085852</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1206,7 +1206,7 @@
     <t>The laterality of the (possibly paired) anatomic structures examined. E.g., the left knee, both lungs, or unpaired abdomen. If present, shall be consistent with any laterality information indicated in ImagingStudy.series.bodySite.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modificateur-topographique-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modificateur-topographique-cisis|20260716085851</t>
   </si>
   <si>
     <t>(0020,0060)</t>
@@ -1403,7 +1403,7 @@
     <t>DICOM instance  type.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-sop-class-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-sop-class-cisis|20260716085851</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP]. source[classCode=OBS, moodCode=EVN, code="sop class"].value</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T14:37:13+00:00</t>
+    <t>2026-08-25T08:25:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T08:25:54+00:00</t>
+    <t>2026-08-25T13:09:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:09:33+00:00</t>
+    <t>2026-08-25T13:40:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:40:20+00:00</t>
+    <t>2026-08-25T14:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T14:52:49+00:00</t>
+    <t>2026-08-26T13:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:43:53+00:00</t>
+    <t>2026-08-26T14:38:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T14:38:07+00:00</t>
+    <t>2026-08-27T07:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
